--- a/artfynd/A 45868-2023 artfynd.xlsx
+++ b/artfynd/A 45868-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830435</v>
       </c>
       <c r="B2" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>125830436</v>
       </c>
       <c r="B4" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125830421</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125830425</v>
       </c>
       <c r="B7" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45868-2023 artfynd.xlsx
+++ b/artfynd/A 45868-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830435</v>
       </c>
       <c r="B2" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125830415</v>
       </c>
       <c r="B3" t="n">
-        <v>57781</v>
+        <v>57782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>125830436</v>
       </c>
       <c r="B4" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>125830407</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125830421</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125830425</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45868-2023 artfynd.xlsx
+++ b/artfynd/A 45868-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830435</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125830415</v>
       </c>
       <c r="B3" t="n">
-        <v>57782</v>
+        <v>57786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>125830436</v>
       </c>
       <c r="B4" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>125830407</v>
       </c>
       <c r="B5" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125830421</v>
       </c>
       <c r="B6" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125830425</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45868-2023 artfynd.xlsx
+++ b/artfynd/A 45868-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125830435</v>
       </c>
       <c r="B2" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Litsgård, Johan Karlsson</t>
+          <t>Johan Karlsson, Fredrik Litsgård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -797,7 +797,7 @@
         <v>125830415</v>
       </c>
       <c r="B3" t="n">
-        <v>57786</v>
+        <v>57787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Litsgård, Johan Karlsson</t>
+          <t>Johan Karlsson, Fredrik Litsgård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -916,7 +916,7 @@
         <v>125830436</v>
       </c>
       <c r="B4" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Litsgård, Johan Karlsson</t>
+          <t>Johan Karlsson, Fredrik Litsgård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>125830407</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125830421</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Litsgård, Johan Karlsson</t>
+          <t>Johan Karlsson, Fredrik Litsgård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
         <v>125830425</v>
       </c>
       <c r="B7" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Litsgård, Johan Karlsson</t>
+          <t>Johan Karlsson, Fredrik Litsgård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
